--- a/artfynd/A 54177-2024 artfynd.xlsx
+++ b/artfynd/A 54177-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122397210</v>
+        <v>122396736</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,16 +935,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562897</v>
+        <v>562985</v>
       </c>
       <c r="R4" t="n">
-        <v>7040625</v>
+        <v>7040545</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122396997</v>
+        <v>122396615</v>
       </c>
       <c r="B5" t="n">
-        <v>56584</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,41 +1048,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1096,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562971</v>
+        <v>562936</v>
       </c>
       <c r="R5" t="n">
-        <v>7040589</v>
+        <v>7040526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122396615</v>
+        <v>122396997</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>56584</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,31 +1165,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1213,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562936</v>
+        <v>562971</v>
       </c>
       <c r="R6" t="n">
-        <v>7040526</v>
+        <v>7040589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122396736</v>
+        <v>122397210</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,16 +1296,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1330,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562985</v>
+        <v>562897</v>
       </c>
       <c r="R7" t="n">
-        <v>7040545</v>
+        <v>7040625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1370,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54177-2024 artfynd.xlsx
+++ b/artfynd/A 54177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122397361</v>
+        <v>122396997</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>56584</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +730,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562889</v>
+        <v>562971</v>
       </c>
       <c r="R2" t="n">
-        <v>7040619</v>
+        <v>7040589</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +765,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +775,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -919,7 +924,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122396736</v>
+        <v>122396615</v>
       </c>
       <c r="B4" t="n">
         <v>57390</v>
@@ -964,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562985</v>
+        <v>562936</v>
       </c>
       <c r="R4" t="n">
-        <v>7040545</v>
+        <v>7040526</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122396615</v>
+        <v>122396736</v>
       </c>
       <c r="B5" t="n">
         <v>57390</v>
@@ -1081,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562936</v>
+        <v>562985</v>
       </c>
       <c r="R5" t="n">
-        <v>7040526</v>
+        <v>7040545</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122396997</v>
+        <v>122397210</v>
       </c>
       <c r="B6" t="n">
-        <v>56584</v>
+        <v>57374</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,41 +1170,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562971</v>
+        <v>562897</v>
       </c>
       <c r="R6" t="n">
-        <v>7040589</v>
+        <v>7040625</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1248,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122397210</v>
+        <v>122397361</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1316,7 +1316,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562897</v>
+        <v>562889</v>
       </c>
       <c r="R7" t="n">
-        <v>7040625</v>
+        <v>7040619</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 54177-2024 artfynd.xlsx
+++ b/artfynd/A 54177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122396997</v>
+        <v>122396736</v>
       </c>
       <c r="B2" t="n">
-        <v>56584</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -730,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562971</v>
+        <v>562985</v>
       </c>
       <c r="R2" t="n">
-        <v>7040589</v>
+        <v>7040545</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -775,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,7 +795,7 @@
         <v>122397277</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -924,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122396615</v>
+        <v>122397361</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,16 +930,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -960,7 +950,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562936</v>
+        <v>562889</v>
       </c>
       <c r="R4" t="n">
-        <v>7040526</v>
+        <v>7040619</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1004,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122396736</v>
+        <v>122396615</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562985</v>
+        <v>562936</v>
       </c>
       <c r="R5" t="n">
-        <v>7040545</v>
+        <v>7040526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122397210</v>
+        <v>122396997</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>56589</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,31 +1165,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1203,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562897</v>
+        <v>562971</v>
       </c>
       <c r="R6" t="n">
-        <v>7040625</v>
+        <v>7040589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,12 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122397361</v>
+        <v>122397210</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562889</v>
+        <v>562897</v>
       </c>
       <c r="R7" t="n">
-        <v>7040619</v>
+        <v>7040625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 54177-2024 artfynd.xlsx
+++ b/artfynd/A 54177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122396736</v>
+        <v>122397210</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562985</v>
+        <v>562897</v>
       </c>
       <c r="R2" t="n">
-        <v>7040545</v>
+        <v>7040625</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122397277</v>
+        <v>122396997</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>56589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,31 +809,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562894</v>
+        <v>562971</v>
       </c>
       <c r="R3" t="n">
-        <v>7040632</v>
+        <v>7040589</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1036,7 +1046,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122396615</v>
+        <v>122396736</v>
       </c>
       <c r="B5" t="n">
         <v>57395</v>
@@ -1081,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562936</v>
+        <v>562985</v>
       </c>
       <c r="R5" t="n">
-        <v>7040526</v>
+        <v>7040545</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122396997</v>
+        <v>122396615</v>
       </c>
       <c r="B6" t="n">
-        <v>56589</v>
+        <v>57395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,41 +1175,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562971</v>
+        <v>562936</v>
       </c>
       <c r="R6" t="n">
-        <v>7040589</v>
+        <v>7040526</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122397210</v>
+        <v>122397277</v>
       </c>
       <c r="B7" t="n">
         <v>57379</v>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562897</v>
+        <v>562894</v>
       </c>
       <c r="R7" t="n">
-        <v>7040625</v>
+        <v>7040632</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 54177-2024 artfynd.xlsx
+++ b/artfynd/A 54177-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122397210</v>
+        <v>122397277</v>
       </c>
       <c r="B2" t="n">
         <v>57379</v>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100109</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562897</v>
+        <v>562894</v>
       </c>
       <c r="R2" t="n">
-        <v>7040625</v>
+        <v>7040632</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122396997</v>
+        <v>122397210</v>
       </c>
       <c r="B3" t="n">
-        <v>56589</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,41 +804,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -852,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562971</v>
+        <v>562897</v>
       </c>
       <c r="R3" t="n">
-        <v>7040589</v>
+        <v>7040625</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122397361</v>
+        <v>122396997</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>56589</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,31 +921,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>100138</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562889</v>
+        <v>562971</v>
       </c>
       <c r="R4" t="n">
-        <v>7040619</v>
+        <v>7040589</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122396736</v>
+        <v>122396615</v>
       </c>
       <c r="B5" t="n">
         <v>57395</v>
@@ -1064,11 +1049,6 @@
       <c r="E5" t="n">
         <v>100049</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1091,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562985</v>
+        <v>562936</v>
       </c>
       <c r="R5" t="n">
-        <v>7040545</v>
+        <v>7040526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122396615</v>
+        <v>122396736</v>
       </c>
       <c r="B6" t="n">
         <v>57395</v>
@@ -1181,11 +1161,6 @@
       <c r="E6" t="n">
         <v>100049</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1208,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562936</v>
+        <v>562985</v>
       </c>
       <c r="R6" t="n">
-        <v>7040526</v>
+        <v>7040545</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122397277</v>
+        <v>122397361</v>
       </c>
       <c r="B7" t="n">
         <v>57379</v>
@@ -1298,11 +1273,6 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1316,7 +1286,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1325,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562894</v>
+        <v>562889</v>
       </c>
       <c r="R7" t="n">
-        <v>7040632</v>
+        <v>7040619</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 54177-2024 artfynd.xlsx
+++ b/artfynd/A 54177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122397277</v>
+        <v>122396615</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,11 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562894</v>
+        <v>562936</v>
       </c>
       <c r="R2" t="n">
-        <v>7040632</v>
+        <v>7040526</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122397210</v>
+        <v>122396997</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>56593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,26 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562897</v>
+        <v>562971</v>
       </c>
       <c r="R3" t="n">
-        <v>7040625</v>
+        <v>7040589</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122396997</v>
+        <v>122397361</v>
       </c>
       <c r="B4" t="n">
-        <v>56589</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,36 +931,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562971</v>
+        <v>562889</v>
       </c>
       <c r="R4" t="n">
-        <v>7040589</v>
+        <v>7040619</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122396615</v>
+        <v>122397277</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,11 +1057,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1071,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562936</v>
+        <v>562894</v>
       </c>
       <c r="R5" t="n">
-        <v>7040526</v>
+        <v>7040632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,7 +1166,7 @@
         <v>122396736</v>
       </c>
       <c r="B6" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,6 +1180,11 @@
       </c>
       <c r="E6" t="n">
         <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1255,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122397361</v>
+        <v>122397210</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,6 +1298,11 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1286,7 +1316,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1295,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562889</v>
+        <v>562897</v>
       </c>
       <c r="R7" t="n">
-        <v>7040619</v>
+        <v>7040625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 54177-2024 artfynd.xlsx
+++ b/artfynd/A 54177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122396615</v>
+        <v>122396997</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>56593</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +730,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562936</v>
+        <v>562971</v>
       </c>
       <c r="R2" t="n">
-        <v>7040526</v>
+        <v>7040589</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +765,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +775,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122396997</v>
+        <v>122396615</v>
       </c>
       <c r="B3" t="n">
-        <v>56593</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,41 +814,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562971</v>
+        <v>562936</v>
       </c>
       <c r="R3" t="n">
-        <v>7040589</v>
+        <v>7040526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122397361</v>
+        <v>122397210</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -955,7 +955,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562889</v>
+        <v>562897</v>
       </c>
       <c r="R4" t="n">
-        <v>7040619</v>
+        <v>7040625</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1041,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122397277</v>
+        <v>122397361</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1077,7 +1077,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562894</v>
+        <v>562889</v>
       </c>
       <c r="R5" t="n">
-        <v>7040632</v>
+        <v>7040619</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1280,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122397210</v>
+        <v>122397277</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562897</v>
+        <v>562894</v>
       </c>
       <c r="R7" t="n">
-        <v>7040625</v>
+        <v>7040632</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 54177-2024 artfynd.xlsx
+++ b/artfynd/A 54177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122396997</v>
+        <v>122397361</v>
       </c>
       <c r="B2" t="n">
-        <v>56593</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -730,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562971</v>
+        <v>562889</v>
       </c>
       <c r="R2" t="n">
-        <v>7040589</v>
+        <v>7040619</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -775,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122396615</v>
+        <v>122397277</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,16 +813,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -847,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562936</v>
+        <v>562894</v>
       </c>
       <c r="R3" t="n">
-        <v>7040526</v>
+        <v>7040632</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122397210</v>
+        <v>122396736</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,16 +935,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562897</v>
+        <v>562985</v>
       </c>
       <c r="R4" t="n">
-        <v>7040625</v>
+        <v>7040545</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122397361</v>
+        <v>122396615</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,16 +1052,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1077,7 +1072,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1086,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562889</v>
+        <v>562936</v>
       </c>
       <c r="R5" t="n">
-        <v>7040619</v>
+        <v>7040526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122396736</v>
+        <v>122397210</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,16 +1169,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1208,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562985</v>
+        <v>562897</v>
       </c>
       <c r="R6" t="n">
-        <v>7040545</v>
+        <v>7040625</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122397277</v>
+        <v>122396997</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>56593</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,31 +1287,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1325,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562894</v>
+        <v>562971</v>
       </c>
       <c r="R7" t="n">
-        <v>7040632</v>
+        <v>7040589</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,12 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54177-2024 artfynd.xlsx
+++ b/artfynd/A 54177-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122397361</v>
+        <v>122397210</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562889</v>
+        <v>562897</v>
       </c>
       <c r="R2" t="n">
-        <v>7040619</v>
+        <v>7040625</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122397277</v>
+        <v>122396736</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562894</v>
+        <v>562985</v>
       </c>
       <c r="R3" t="n">
-        <v>7040632</v>
+        <v>7040545</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122396736</v>
+        <v>122396997</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>56593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,31 +926,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562985</v>
+        <v>562971</v>
       </c>
       <c r="R4" t="n">
-        <v>7040545</v>
+        <v>7040589</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122396615</v>
+        <v>122397361</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,16 +1057,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1072,7 +1077,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1081,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562936</v>
+        <v>562889</v>
       </c>
       <c r="R5" t="n">
-        <v>7040526</v>
+        <v>7040619</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122397210</v>
+        <v>122396615</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,16 +1179,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1198,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562897</v>
+        <v>562936</v>
       </c>
       <c r="R6" t="n">
-        <v>7040625</v>
+        <v>7040526</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122396997</v>
+        <v>122397277</v>
       </c>
       <c r="B7" t="n">
-        <v>56593</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,41 +1292,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1330,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562971</v>
+        <v>562894</v>
       </c>
       <c r="R7" t="n">
-        <v>7040589</v>
+        <v>7040632</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1370,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54177-2024 artfynd.xlsx
+++ b/artfynd/A 54177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122397210</v>
+        <v>122396997</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>56593</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +730,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562897</v>
+        <v>562971</v>
       </c>
       <c r="R2" t="n">
-        <v>7040625</v>
+        <v>7040589</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +765,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +775,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122396736</v>
+        <v>122396615</v>
       </c>
       <c r="B3" t="n">
         <v>57399</v>
@@ -842,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562985</v>
+        <v>562936</v>
       </c>
       <c r="R3" t="n">
-        <v>7040545</v>
+        <v>7040526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122396997</v>
+        <v>122397361</v>
       </c>
       <c r="B4" t="n">
-        <v>56593</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,41 +931,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562971</v>
+        <v>562889</v>
       </c>
       <c r="R4" t="n">
-        <v>7040589</v>
+        <v>7040619</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122397361</v>
+        <v>122396736</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,16 +1057,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1077,7 +1077,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562889</v>
+        <v>562985</v>
       </c>
       <c r="R5" t="n">
-        <v>7040619</v>
+        <v>7040545</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122396615</v>
+        <v>122397210</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,16 +1174,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1208,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562936</v>
+        <v>562897</v>
       </c>
       <c r="R6" t="n">
-        <v>7040526</v>
+        <v>7040625</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1248,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 54177-2024 artfynd.xlsx
+++ b/artfynd/A 54177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122396997</v>
+        <v>122397277</v>
       </c>
       <c r="B2" t="n">
-        <v>56593</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -730,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562971</v>
+        <v>562894</v>
       </c>
       <c r="R2" t="n">
-        <v>7040589</v>
+        <v>7040632</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -775,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122396615</v>
+        <v>122397361</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,16 +813,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,7 +833,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -847,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562936</v>
+        <v>562889</v>
       </c>
       <c r="R3" t="n">
-        <v>7040526</v>
+        <v>7040619</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122397361</v>
+        <v>122397210</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562889</v>
+        <v>562897</v>
       </c>
       <c r="R4" t="n">
-        <v>7040619</v>
+        <v>7040625</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1044,7 +1044,7 @@
         <v>122396736</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122397210</v>
+        <v>122396997</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>56594</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,31 +1170,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1203,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562897</v>
+        <v>562971</v>
       </c>
       <c r="R6" t="n">
-        <v>7040625</v>
+        <v>7040589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1248,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,12 +1258,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122397277</v>
+        <v>122396615</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>57400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,16 +1301,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1325,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562894</v>
+        <v>562936</v>
       </c>
       <c r="R7" t="n">
-        <v>7040632</v>
+        <v>7040526</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,12 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54177-2024 artfynd.xlsx
+++ b/artfynd/A 54177-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122397277</v>
+        <v>122397361</v>
       </c>
       <c r="B2" t="n">
         <v>57384</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562894</v>
+        <v>562889</v>
       </c>
       <c r="R2" t="n">
-        <v>7040632</v>
+        <v>7040619</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122397361</v>
+        <v>122396615</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,7 +833,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562889</v>
+        <v>562936</v>
       </c>
       <c r="R3" t="n">
-        <v>7040619</v>
+        <v>7040526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122397210</v>
+        <v>122396997</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>56594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,31 +926,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562897</v>
+        <v>562971</v>
       </c>
       <c r="R4" t="n">
-        <v>7040625</v>
+        <v>7040589</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122396736</v>
+        <v>122397277</v>
       </c>
       <c r="B5" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,16 +1057,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562985</v>
+        <v>562894</v>
       </c>
       <c r="R5" t="n">
-        <v>7040545</v>
+        <v>7040632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122396997</v>
+        <v>122396736</v>
       </c>
       <c r="B6" t="n">
-        <v>56594</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,41 +1175,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1213,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562971</v>
+        <v>562985</v>
       </c>
       <c r="R6" t="n">
-        <v>7040589</v>
+        <v>7040545</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122396615</v>
+        <v>122397210</v>
       </c>
       <c r="B7" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,16 +1296,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1330,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562936</v>
+        <v>562897</v>
       </c>
       <c r="R7" t="n">
-        <v>7040526</v>
+        <v>7040625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1370,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54177-2024 artfynd.xlsx
+++ b/artfynd/A 54177-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122397361</v>
+        <v>122397210</v>
       </c>
       <c r="B2" t="n">
         <v>57384</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562889</v>
+        <v>562897</v>
       </c>
       <c r="R2" t="n">
-        <v>7040619</v>
+        <v>7040625</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122396615</v>
+        <v>122397277</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562936</v>
+        <v>562894</v>
       </c>
       <c r="R3" t="n">
-        <v>7040526</v>
+        <v>7040632</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122396997</v>
+        <v>122396615</v>
       </c>
       <c r="B4" t="n">
-        <v>56594</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,41 +931,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562971</v>
+        <v>562936</v>
       </c>
       <c r="R4" t="n">
-        <v>7040589</v>
+        <v>7040526</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122397277</v>
+        <v>122396736</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,16 +1052,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1086,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562894</v>
+        <v>562985</v>
       </c>
       <c r="R5" t="n">
-        <v>7040632</v>
+        <v>7040545</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122396736</v>
+        <v>122396997</v>
       </c>
       <c r="B6" t="n">
-        <v>57400</v>
+        <v>56594</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,31 +1165,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562985</v>
+        <v>562971</v>
       </c>
       <c r="R6" t="n">
-        <v>7040545</v>
+        <v>7040589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122397210</v>
+        <v>122397361</v>
       </c>
       <c r="B7" t="n">
         <v>57384</v>
@@ -1316,7 +1316,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562897</v>
+        <v>562889</v>
       </c>
       <c r="R7" t="n">
-        <v>7040625</v>
+        <v>7040619</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
